--- a/output/pdf_financials_xlsx/MIVO.xlsx
+++ b/output/pdf_financials_xlsx/MIVO.xlsx
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.041883</v>
       </c>
     </row>
     <row r="93">
@@ -7095,7 +7095,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MIVO.xlsx
+++ b/output/pdf_financials_xlsx/MIVO.xlsx
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
     </row>
     <row r="13">
@@ -1597,7 +1597,7 @@
         <v>-0.040731</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.724511</v>
+        <v>-0.724756</v>
       </c>
     </row>
     <row r="28">
@@ -1681,7 +1681,7 @@
         <v>-0.040731</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.724511</v>
+        <v>-0.724756</v>
       </c>
     </row>
     <row r="30">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-31762.86716352477</v>
+        <v>-31773.60806663744</v>
       </c>
     </row>
     <row r="31">
@@ -1859,22 +1859,22 @@
         <v>0.336612</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.229858</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.141971</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.06413199999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.0257</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.024902</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.683773</v>
       </c>
     </row>
     <row r="35">
@@ -1939,22 +1939,22 @@
         <v>0.455846</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.190811</v>
+        <v>0.420669</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.144157</v>
+        <v>0.286128</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.060622</v>
+        <v>0.124754</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.007813000000000001</v>
+        <v>0.033513</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.01209</v>
+        <v>0.036992</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.001425</v>
+        <v>0.685198</v>
       </c>
     </row>
     <row r="37">
@@ -2419,22 +2419,22 @@
         <v>0.000375</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.229858</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.141971</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.06413199999999999</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.0257</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.032467</v>
+        <v>0.007565</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.6895019999999999</v>
+        <v>0.005729</v>
       </c>
     </row>
     <row r="49">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">

--- a/output/pdf_financials_xlsx/MIVO.xlsx
+++ b/output/pdf_financials_xlsx/MIVO.xlsx
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.016306</v>
+        <v>0.044966</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.017305</v>
+        <v>0.041465</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.003622</v>
+        <v>0.011866</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0.000868</v>
@@ -19285,7 +19285,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MIVO.xlsx
+++ b/output/pdf_financials_xlsx/MIVO.xlsx
@@ -3112,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.011996</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000431</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.000871</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.006893</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -3232,25 +3232,25 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0122</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0756</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.08651499999999999</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.08910800000000001</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.063404</v>
       </c>
     </row>
     <row r="68">
@@ -5228,34 +5228,34 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.530726</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.31353</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.432991</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.304314</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.188855</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.092708</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.039874</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.008319</v>
       </c>
     </row>
     <row r="116">
@@ -10284,7 +10284,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -10493,7 +10497,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -11763,7 +11771,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -11964,7 +11976,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -13161,7 +13177,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
